--- a/wolf/Excel/Ear_耳朵.xlsx
+++ b/wolf/Excel/Ear_耳朵.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="500"/>
+    <workbookView windowWidth="24750" windowHeight="12060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="132">
   <si>
     <t>Int</t>
   </si>
@@ -64,6 +64,9 @@
     <t>0|0|0|0|0|0|1|1|1</t>
   </si>
   <si>
+    <t>0|0|20|0|0|0|1|1|1</t>
+  </si>
+  <si>
     <t>围巾</t>
   </si>
   <si>
@@ -134,9 +137,6 @@
   </si>
   <si>
     <t>蝙蝠</t>
-  </si>
-  <si>
-    <t>0|0|20|0|0|0|1|1|1</t>
   </si>
   <si>
     <t>花瓣环绕</t>
@@ -1073,7 +1073,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1107,9 +1107,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1644,7 +1641,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U218"/>
+  <dimension ref="A1:U219"/>
   <sheetFormatPr defaultColWidth="12.025" defaultRowHeight="16.5"/>
   <cols>
     <col min="3" max="3" width="35.125" customWidth="1"/>
@@ -1802,14 +1799,12 @@
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="1">
+        <v>677382</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="C6" s="1">
-        <v>295506</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -1839,7 +1834,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="1">
-        <v>352615</v>
+        <v>295506</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>10</v>
@@ -1872,9 +1867,9 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>404433</v>
-      </c>
-      <c r="D8" s="1" t="s">
+        <v>352615</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1">
@@ -1905,9 +1900,9 @@
         <v>14</v>
       </c>
       <c r="C9" s="1">
-        <v>404473</v>
-      </c>
-      <c r="D9" s="4" t="s">
+        <v>404433</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1">
@@ -1938,7 +1933,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="1">
-        <v>441348</v>
+        <v>404473</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -1963,18 +1958,18 @@
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
     </row>
-    <row r="11" ht="17.25" spans="1:21">
+    <row r="11" spans="1:21">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="5">
-        <v>142935</v>
+      <c r="C11" s="1">
+        <v>441348</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -1996,18 +1991,18 @@
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" ht="17.25" spans="1:21">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5">
+        <v>142935</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="C12" s="1">
-        <v>462790</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -2034,13 +2029,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>462790</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="C13" s="1">
-        <v>462791</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -2070,10 +2065,10 @@
         <v>21</v>
       </c>
       <c r="C14" s="1">
-        <v>441349</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>10</v>
+        <v>462791</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -2100,13 +2095,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1">
-        <v>13728</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>22</v>
+        <v>441349</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
@@ -2132,16 +2127,16 @@
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="1">
+        <v>13728</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="7">
-        <v>169404</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="7">
+      <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1"/>
@@ -2165,13 +2160,13 @@
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="1">
-        <v>200911</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="B17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="7">
+        <v>169404</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="7">
@@ -2199,13 +2194,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="1">
+        <v>200911</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C18" s="1">
-        <v>88831</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E18" s="7">
         <v>0</v>
@@ -2232,13 +2227,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1">
-        <v>88818</v>
+        <v>88831</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E19" s="7">
         <v>0</v>
@@ -2265,12 +2260,12 @@
         <v>16</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="1">
-        <v>88825</v>
-      </c>
-      <c r="D20" s="9" t="s">
+        <v>88818</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="7">
@@ -2298,13 +2293,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="1">
+        <v>88825</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="C21" s="1">
-        <v>287819</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="E21" s="7">
         <v>0</v>
@@ -2331,13 +2326,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="1">
+        <v>287819</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C22" s="1">
-        <v>26155</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="E22" s="7">
         <v>0</v>
@@ -2364,15 +2359,15 @@
         <v>19</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1">
+        <v>26155</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="1">
-        <v>451246</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="1">
+      <c r="E23" s="7">
         <v>0</v>
       </c>
       <c r="F23" s="1"/>
@@ -2400,10 +2395,10 @@
         <v>34</v>
       </c>
       <c r="C24" s="1">
-        <v>452716</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>35</v>
+        <v>451246</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
@@ -2430,13 +2425,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="1">
-        <v>340179</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>10</v>
+        <v>452716</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -2462,9 +2457,11 @@
       <c r="A26" s="1">
         <v>22</v>
       </c>
-      <c r="B26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="C26" s="1">
-        <v>340181</v>
+        <v>340179</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>10</v>
@@ -2493,11 +2490,9 @@
       <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="B27" s="3"/>
       <c r="C27" s="1">
-        <v>295800</v>
+        <v>340181</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>10</v>
@@ -2527,10 +2522,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C28" s="1">
-        <v>235888</v>
+        <v>295800</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
@@ -2560,10 +2555,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1">
-        <v>295801</v>
+        <v>235888</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>10</v>
@@ -2593,13 +2588,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30" s="1">
-        <v>26158</v>
+        <v>295801</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
@@ -2626,13 +2621,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31" s="1">
-        <v>184435</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>42</v>
+        <v>26158</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
@@ -2659,13 +2654,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C32" s="1">
-        <v>452232</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>10</v>
+        <v>184435</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
@@ -2695,7 +2690,7 @@
         <v>43</v>
       </c>
       <c r="C33" s="1">
-        <v>452233</v>
+        <v>452232</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>10</v>
@@ -2728,9 +2723,9 @@
         <v>43</v>
       </c>
       <c r="C34" s="1">
-        <v>452234</v>
-      </c>
-      <c r="D34" s="1" t="s">
+        <v>452233</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="1">
@@ -2761,9 +2756,9 @@
         <v>43</v>
       </c>
       <c r="C35" s="1">
-        <v>452235</v>
-      </c>
-      <c r="D35" s="4" t="s">
+        <v>452234</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="1">
@@ -2791,10 +2786,10 @@
         <v>32</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" s="1">
-        <v>471540</v>
+        <v>452235</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>10</v>
@@ -2827,9 +2822,9 @@
         <v>44</v>
       </c>
       <c r="C37" s="1">
-        <v>471541</v>
-      </c>
-      <c r="D37" s="1" t="s">
+        <v>471540</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="1">
@@ -2860,9 +2855,9 @@
         <v>44</v>
       </c>
       <c r="C38" s="1">
-        <v>471542</v>
-      </c>
-      <c r="D38" s="4" t="s">
+        <v>471541</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="1">
@@ -2893,7 +2888,7 @@
         <v>44</v>
       </c>
       <c r="C39" s="1">
-        <v>471543</v>
+        <v>471542</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>10</v>
@@ -2923,12 +2918,12 @@
         <v>36</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" s="1">
-        <v>502350</v>
-      </c>
-      <c r="D40" s="1" t="s">
+        <v>471543</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="1">
@@ -2956,15 +2951,15 @@
         <v>37</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" s="1">
-        <v>502351</v>
-      </c>
-      <c r="D41" s="4" t="s">
+        <v>502350</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="1">
         <v>0</v>
       </c>
       <c r="F41" s="1"/>
@@ -2989,10 +2984,10 @@
         <v>38</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C42" s="1">
-        <v>502352</v>
+        <v>502351</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>10</v>
@@ -3022,13 +3017,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43" s="1">
-        <v>266596</v>
+        <v>502352</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E43" s="7">
         <v>0</v>
@@ -3058,7 +3053,7 @@
         <v>48</v>
       </c>
       <c r="C44" s="1">
-        <v>266597</v>
+        <v>266596</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>49</v>
@@ -3091,7 +3086,7 @@
         <v>48</v>
       </c>
       <c r="C45" s="1">
-        <v>266598</v>
+        <v>266597</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>49</v>
@@ -3124,7 +3119,7 @@
         <v>48</v>
       </c>
       <c r="C46" s="1">
-        <v>266600</v>
+        <v>266598</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>49</v>
@@ -3157,7 +3152,7 @@
         <v>48</v>
       </c>
       <c r="C47" s="1">
-        <v>266601</v>
+        <v>266600</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>49</v>
@@ -3190,12 +3185,12 @@
         <v>48</v>
       </c>
       <c r="C48" s="1">
-        <v>266602</v>
+        <v>266601</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="7">
         <v>0</v>
       </c>
       <c r="F48" s="1"/>
@@ -3223,7 +3218,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="1">
-        <v>266610</v>
+        <v>266602</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>49</v>
@@ -3253,13 +3248,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C50" s="1">
-        <v>467603</v>
+        <v>266610</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
@@ -3286,13 +3281,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C51" s="1">
-        <v>266332</v>
+        <v>467603</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
@@ -3319,13 +3314,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C52" s="1">
-        <v>457013</v>
+        <v>266332</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E52" s="1">
         <v>0</v>
@@ -3352,13 +3347,13 @@
         <v>49</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C53" s="1">
-        <v>209534</v>
+        <v>457013</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -3385,13 +3380,13 @@
         <v>50</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C54" s="1">
-        <v>112801</v>
+        <v>209534</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E54" s="1">
         <v>0</v>
@@ -3418,13 +3413,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C55" s="1">
-        <v>173867</v>
+        <v>112801</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
@@ -3450,14 +3445,14 @@
       <c r="A56" s="1">
         <v>52</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>62</v>
+      <c r="B56" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C56" s="1">
-        <v>26146</v>
+        <v>173867</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
@@ -3484,13 +3479,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C57" s="1">
-        <v>26151</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>10</v>
+        <v>26146</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
@@ -3516,12 +3511,14 @@
       <c r="A58" s="1">
         <v>54</v>
       </c>
-      <c r="B58" s="1"/>
+      <c r="B58" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="C58" s="1">
-        <v>26155</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>63</v>
+        <v>26151</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -3547,11 +3544,9 @@
       <c r="A59" s="1">
         <v>55</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>65</v>
-      </c>
+      <c r="B59" s="1"/>
       <c r="C59" s="1">
-        <v>160743</v>
+        <v>26155</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>63</v>
@@ -3581,13 +3576,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C60" s="1">
-        <v>162012</v>
+        <v>160743</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3614,13 +3609,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C61" s="1">
-        <v>168959</v>
+        <v>162012</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3647,13 +3642,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62" s="1">
-        <v>200925</v>
+        <v>168959</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3680,13 +3675,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C63" s="1">
-        <v>403000</v>
+        <v>200925</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -3716,7 +3711,7 @@
         <v>69</v>
       </c>
       <c r="C64" s="1">
-        <v>403004</v>
+        <v>403000</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>10</v>
@@ -3749,7 +3744,7 @@
         <v>69</v>
       </c>
       <c r="C65" s="1">
-        <v>403012</v>
+        <v>403004</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>10</v>
@@ -3782,12 +3777,12 @@
         <v>69</v>
       </c>
       <c r="C66" s="1">
-        <v>403014</v>
+        <v>403012</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E66" s="7">
+      <c r="E66" s="1">
         <v>0</v>
       </c>
       <c r="F66" s="1"/>
@@ -3815,7 +3810,7 @@
         <v>69</v>
       </c>
       <c r="C67" s="1">
-        <v>403015</v>
+        <v>403014</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>10</v>
@@ -3845,10 +3840,10 @@
         <v>64</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C68" s="1">
-        <v>506842</v>
+        <v>403015</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>10</v>
@@ -3878,13 +3873,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C69" s="1">
-        <v>442771</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>72</v>
+        <v>506842</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E69" s="7">
         <v>0</v>
@@ -3910,14 +3905,14 @@
       <c r="A70" s="1">
         <v>66</v>
       </c>
-      <c r="B70" s="11" t="s">
-        <v>73</v>
+      <c r="B70" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="C70" s="1">
-        <v>234390</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>74</v>
+        <v>442771</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>72</v>
       </c>
       <c r="E70" s="7">
         <v>0</v>
@@ -3943,12 +3938,14 @@
       <c r="A71" s="1">
         <v>67</v>
       </c>
-      <c r="B71" s="1"/>
+      <c r="B71" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="C71" s="1">
-        <v>292089</v>
+        <v>234390</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="E71" s="7">
         <v>0</v>
@@ -3970,16 +3967,16 @@
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
     </row>
-    <row r="72" ht="17.25" spans="1:21">
+    <row r="72" spans="1:21">
       <c r="A72" s="1">
         <v>68</v>
       </c>
       <c r="B72" s="1"/>
-      <c r="C72" s="12">
-        <v>72681</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>30</v>
+      <c r="C72" s="1">
+        <v>292089</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E72" s="7">
         <v>0</v>
@@ -4006,13 +4003,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="1"/>
-      <c r="C73" s="12">
-        <v>72689</v>
+      <c r="C73" s="5">
+        <v>72681</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E73" s="1">
+        <v>31</v>
+      </c>
+      <c r="E73" s="7">
         <v>0</v>
       </c>
       <c r="F73" s="1"/>
@@ -4037,11 +4034,11 @@
         <v>70</v>
       </c>
       <c r="B74" s="1"/>
-      <c r="C74" s="12">
-        <v>44268</v>
+      <c r="C74" s="5">
+        <v>72689</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
@@ -4068,11 +4065,11 @@
         <v>71</v>
       </c>
       <c r="B75" s="1"/>
-      <c r="C75" s="12">
-        <v>72675</v>
+      <c r="C75" s="5">
+        <v>44268</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
@@ -4099,11 +4096,11 @@
         <v>72</v>
       </c>
       <c r="B76" s="1"/>
-      <c r="C76" s="12">
-        <v>68413</v>
+      <c r="C76" s="5">
+        <v>72675</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
@@ -4130,11 +4127,11 @@
         <v>73</v>
       </c>
       <c r="B77" s="1"/>
-      <c r="C77" s="12">
-        <v>266331</v>
+      <c r="C77" s="5">
+        <v>68413</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
@@ -4161,11 +4158,11 @@
         <v>74</v>
       </c>
       <c r="B78" s="1"/>
-      <c r="C78" s="12">
-        <v>386337</v>
+      <c r="C78" s="5">
+        <v>266331</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="E78" s="1">
         <v>0</v>
@@ -4192,11 +4189,11 @@
         <v>75</v>
       </c>
       <c r="B79" s="1"/>
-      <c r="C79" s="12">
-        <v>173237</v>
+      <c r="C79" s="5">
+        <v>386337</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E79" s="1">
         <v>0</v>
@@ -4223,8 +4220,8 @@
         <v>76</v>
       </c>
       <c r="B80" s="1"/>
-      <c r="C80" s="12">
-        <v>173239</v>
+      <c r="C80" s="5">
+        <v>173237</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>79</v>
@@ -4254,8 +4251,8 @@
         <v>77</v>
       </c>
       <c r="B81" s="1"/>
-      <c r="C81" s="12">
-        <v>173240</v>
+      <c r="C81" s="5">
+        <v>173239</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>79</v>
@@ -4285,8 +4282,8 @@
         <v>78</v>
       </c>
       <c r="B82" s="1"/>
-      <c r="C82" s="12">
-        <v>173242</v>
+      <c r="C82" s="5">
+        <v>173240</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>79</v>
@@ -4316,8 +4313,8 @@
         <v>79</v>
       </c>
       <c r="B83" s="1"/>
-      <c r="C83" s="12">
-        <v>173241</v>
+      <c r="C83" s="5">
+        <v>173242</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>79</v>
@@ -4347,11 +4344,11 @@
         <v>80</v>
       </c>
       <c r="B84" s="1"/>
-      <c r="C84" s="12">
-        <v>173243</v>
+      <c r="C84" s="5">
+        <v>173241</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
@@ -4378,8 +4375,8 @@
         <v>81</v>
       </c>
       <c r="B85" s="1"/>
-      <c r="C85" s="12">
-        <v>173244</v>
+      <c r="C85" s="5">
+        <v>173243</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>80</v>
@@ -4409,11 +4406,11 @@
         <v>82</v>
       </c>
       <c r="B86" s="1"/>
-      <c r="C86" s="12">
-        <v>173245</v>
+      <c r="C86" s="5">
+        <v>173244</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E86" s="1">
         <v>0</v>
@@ -4440,11 +4437,11 @@
         <v>83</v>
       </c>
       <c r="B87" s="1"/>
-      <c r="C87" s="12">
-        <v>173501</v>
+      <c r="C87" s="5">
+        <v>173245</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E87" s="1">
         <v>0</v>
@@ -4471,11 +4468,11 @@
         <v>84</v>
       </c>
       <c r="B88" s="1"/>
-      <c r="C88" s="12">
-        <v>173502</v>
+      <c r="C88" s="5">
+        <v>173501</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
@@ -4502,8 +4499,8 @@
         <v>85</v>
       </c>
       <c r="B89" s="1"/>
-      <c r="C89" s="12">
-        <v>173499</v>
+      <c r="C89" s="5">
+        <v>173502</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>80</v>
@@ -4533,11 +4530,11 @@
         <v>86</v>
       </c>
       <c r="B90" s="1"/>
-      <c r="C90" s="12">
-        <v>173503</v>
+      <c r="C90" s="5">
+        <v>173499</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E90" s="1">
         <v>0</v>
@@ -4564,13 +4561,13 @@
         <v>87</v>
       </c>
       <c r="B91" s="1"/>
-      <c r="C91" s="12">
-        <v>173504</v>
+      <c r="C91" s="5">
+        <v>173503</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E91" s="7">
+        <v>83</v>
+      </c>
+      <c r="E91" s="1">
         <v>0</v>
       </c>
       <c r="F91" s="1"/>
@@ -4595,11 +4592,11 @@
         <v>88</v>
       </c>
       <c r="B92" s="1"/>
-      <c r="C92" s="12">
-        <v>173505</v>
+      <c r="C92" s="5">
+        <v>173504</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E92" s="7">
         <v>0</v>
@@ -4626,11 +4623,11 @@
         <v>89</v>
       </c>
       <c r="B93" s="1"/>
-      <c r="C93" s="12">
-        <v>173506</v>
+      <c r="C93" s="5">
+        <v>173505</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E93" s="7">
         <v>0</v>
@@ -4657,11 +4654,11 @@
         <v>90</v>
       </c>
       <c r="B94" s="1"/>
-      <c r="C94" s="12">
-        <v>173858</v>
+      <c r="C94" s="5">
+        <v>173506</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E94" s="7">
         <v>0</v>
@@ -4688,11 +4685,11 @@
         <v>91</v>
       </c>
       <c r="B95" s="1"/>
-      <c r="C95" s="12">
-        <v>173859</v>
+      <c r="C95" s="5">
+        <v>173858</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E95" s="7">
         <v>0</v>
@@ -4719,11 +4716,11 @@
         <v>92</v>
       </c>
       <c r="B96" s="1"/>
-      <c r="C96" s="12">
-        <v>173860</v>
+      <c r="C96" s="5">
+        <v>173859</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E96" s="7">
         <v>0</v>
@@ -4750,11 +4747,11 @@
         <v>93</v>
       </c>
       <c r="B97" s="1"/>
-      <c r="C97" s="12">
-        <v>173861</v>
+      <c r="C97" s="5">
+        <v>173860</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E97" s="7">
         <v>0</v>
@@ -4781,13 +4778,13 @@
         <v>94</v>
       </c>
       <c r="B98" s="1"/>
-      <c r="C98" s="12">
-        <v>173862</v>
+      <c r="C98" s="5">
+        <v>173861</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E98" s="1">
+        <v>90</v>
+      </c>
+      <c r="E98" s="7">
         <v>0</v>
       </c>
       <c r="F98" s="1"/>
@@ -4812,11 +4809,11 @@
         <v>95</v>
       </c>
       <c r="B99" s="1"/>
-      <c r="C99" s="12">
-        <v>173863</v>
+      <c r="C99" s="5">
+        <v>173862</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E99" s="1">
         <v>0</v>
@@ -4843,11 +4840,11 @@
         <v>96</v>
       </c>
       <c r="B100" s="1"/>
-      <c r="C100" s="12">
-        <v>173864</v>
+      <c r="C100" s="5">
+        <v>173863</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
@@ -4874,11 +4871,11 @@
         <v>97</v>
       </c>
       <c r="B101" s="1"/>
-      <c r="C101" s="12">
-        <v>173865</v>
+      <c r="C101" s="5">
+        <v>173864</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E101" s="1">
         <v>0</v>
@@ -4905,11 +4902,11 @@
         <v>98</v>
       </c>
       <c r="B102" s="1"/>
-      <c r="C102" s="12">
-        <v>173866</v>
+      <c r="C102" s="5">
+        <v>173865</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E102" s="1">
         <v>0</v>
@@ -4936,11 +4933,11 @@
         <v>99</v>
       </c>
       <c r="B103" s="1"/>
-      <c r="C103" s="12">
-        <v>390761</v>
+      <c r="C103" s="5">
+        <v>173866</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E103" s="1">
         <v>0</v>
@@ -4967,11 +4964,11 @@
         <v>100</v>
       </c>
       <c r="B104" s="1"/>
-      <c r="C104" s="12">
-        <v>314053</v>
+      <c r="C104" s="5">
+        <v>390761</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E104" s="1">
         <v>0</v>
@@ -4998,11 +4995,11 @@
         <v>101</v>
       </c>
       <c r="B105" s="1"/>
-      <c r="C105" s="12">
-        <v>68397</v>
+      <c r="C105" s="5">
+        <v>314053</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E105" s="1">
         <v>0</v>
@@ -5029,11 +5026,11 @@
         <v>102</v>
       </c>
       <c r="B106" s="1"/>
-      <c r="C106" s="12">
-        <v>504881</v>
+      <c r="C106" s="5">
+        <v>68397</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E106" s="1">
         <v>0</v>
@@ -5060,11 +5057,11 @@
         <v>103</v>
       </c>
       <c r="B107" s="1"/>
-      <c r="C107" s="12">
-        <v>68430</v>
+      <c r="C107" s="5">
+        <v>504881</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E107" s="1">
         <v>0</v>
@@ -5091,11 +5088,11 @@
         <v>104</v>
       </c>
       <c r="B108" s="1"/>
-      <c r="C108" s="12">
-        <v>68462</v>
+      <c r="C108" s="5">
+        <v>68430</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="E108" s="1">
         <v>0</v>
@@ -5122,11 +5119,11 @@
         <v>105</v>
       </c>
       <c r="B109" s="1"/>
-      <c r="C109" s="12">
-        <v>68404</v>
+      <c r="C109" s="5">
+        <v>68462</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E109" s="1">
         <v>0</v>
@@ -5153,11 +5150,11 @@
         <v>106</v>
       </c>
       <c r="B110" s="1"/>
-      <c r="C110" s="12">
-        <v>68406</v>
+      <c r="C110" s="5">
+        <v>68404</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E110" s="1">
         <v>0</v>
@@ -5184,11 +5181,11 @@
         <v>107</v>
       </c>
       <c r="B111" s="1"/>
-      <c r="C111" s="12">
-        <v>68410</v>
+      <c r="C111" s="5">
+        <v>68406</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E111" s="1">
         <v>0</v>
@@ -5215,11 +5212,11 @@
         <v>108</v>
       </c>
       <c r="B112" s="1"/>
-      <c r="C112" s="12">
-        <v>68422</v>
+      <c r="C112" s="5">
+        <v>68410</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E112" s="1">
         <v>0</v>
@@ -5246,11 +5243,11 @@
         <v>109</v>
       </c>
       <c r="B113" s="1"/>
-      <c r="C113" s="12">
-        <v>68424</v>
+      <c r="C113" s="5">
+        <v>68422</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E113" s="1">
         <v>0</v>
@@ -5277,11 +5274,11 @@
         <v>110</v>
       </c>
       <c r="B114" s="1"/>
-      <c r="C114" s="12">
-        <v>68427</v>
+      <c r="C114" s="5">
+        <v>68424</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E114" s="1">
         <v>0</v>
@@ -5308,11 +5305,11 @@
         <v>111</v>
       </c>
       <c r="B115" s="1"/>
-      <c r="C115" s="12">
-        <v>68432</v>
+      <c r="C115" s="5">
+        <v>68427</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E115" s="1">
         <v>0</v>
@@ -5339,13 +5336,13 @@
         <v>112</v>
       </c>
       <c r="B116" s="1"/>
-      <c r="C116" s="12">
-        <v>68434</v>
+      <c r="C116" s="5">
+        <v>68432</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E116" s="7">
+        <v>107</v>
+      </c>
+      <c r="E116" s="1">
         <v>0</v>
       </c>
       <c r="F116" s="1"/>
@@ -5370,11 +5367,11 @@
         <v>113</v>
       </c>
       <c r="B117" s="1"/>
-      <c r="C117" s="12">
-        <v>68436</v>
+      <c r="C117" s="5">
+        <v>68434</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E117" s="7">
         <v>0</v>
@@ -5401,11 +5398,11 @@
         <v>114</v>
       </c>
       <c r="B118" s="1"/>
-      <c r="C118" s="12">
-        <v>68438</v>
+      <c r="C118" s="5">
+        <v>68436</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E118" s="7">
         <v>0</v>
@@ -5432,11 +5429,11 @@
         <v>115</v>
       </c>
       <c r="B119" s="1"/>
-      <c r="C119" s="12">
-        <v>68440</v>
+      <c r="C119" s="5">
+        <v>68438</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E119" s="7">
         <v>0</v>
@@ -5463,11 +5460,11 @@
         <v>116</v>
       </c>
       <c r="B120" s="1"/>
-      <c r="C120" s="12">
-        <v>68442</v>
+      <c r="C120" s="5">
+        <v>68440</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E120" s="7">
         <v>0</v>
@@ -5494,11 +5491,11 @@
         <v>117</v>
       </c>
       <c r="B121" s="1"/>
-      <c r="C121" s="12">
-        <v>68447</v>
+      <c r="C121" s="5">
+        <v>68442</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E121" s="7">
         <v>0</v>
@@ -5525,11 +5522,11 @@
         <v>118</v>
       </c>
       <c r="B122" s="1"/>
-      <c r="C122" s="12">
-        <v>68449</v>
+      <c r="C122" s="5">
+        <v>68447</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E122" s="7">
         <v>0</v>
@@ -5556,13 +5553,13 @@
         <v>119</v>
       </c>
       <c r="B123" s="1"/>
-      <c r="C123" s="12">
-        <v>68452</v>
+      <c r="C123" s="5">
+        <v>68449</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E123" s="1">
+        <v>114</v>
+      </c>
+      <c r="E123" s="7">
         <v>0</v>
       </c>
       <c r="F123" s="1"/>
@@ -5587,11 +5584,11 @@
         <v>120</v>
       </c>
       <c r="B124" s="1"/>
-      <c r="C124" s="12">
-        <v>68456</v>
+      <c r="C124" s="5">
+        <v>68452</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E124" s="1">
         <v>0</v>
@@ -5618,11 +5615,11 @@
         <v>121</v>
       </c>
       <c r="B125" s="1"/>
-      <c r="C125" s="12">
-        <v>111667</v>
+      <c r="C125" s="5">
+        <v>68456</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E125" s="1">
         <v>0</v>
@@ -5649,11 +5646,11 @@
         <v>122</v>
       </c>
       <c r="B126" s="1"/>
-      <c r="C126" s="12">
-        <v>111668</v>
+      <c r="C126" s="5">
+        <v>111667</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E126" s="1">
         <v>0</v>
@@ -5680,11 +5677,11 @@
         <v>123</v>
       </c>
       <c r="B127" s="1"/>
-      <c r="C127" s="12">
-        <v>111669</v>
+      <c r="C127" s="5">
+        <v>111668</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E127" s="1">
         <v>0</v>
@@ -5711,11 +5708,11 @@
         <v>124</v>
       </c>
       <c r="B128" s="1"/>
-      <c r="C128" s="12">
-        <v>117848</v>
+      <c r="C128" s="5">
+        <v>111669</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E128" s="1">
         <v>0</v>
@@ -5742,11 +5739,11 @@
         <v>125</v>
       </c>
       <c r="B129" s="1"/>
-      <c r="C129" s="12">
-        <v>134224</v>
+      <c r="C129" s="5">
+        <v>117848</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E129" s="1">
         <v>0</v>
@@ -5773,11 +5770,11 @@
         <v>126</v>
       </c>
       <c r="B130" s="1"/>
-      <c r="C130" s="12">
-        <v>174438</v>
+      <c r="C130" s="5">
+        <v>134224</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -5804,11 +5801,11 @@
         <v>127</v>
       </c>
       <c r="B131" s="1"/>
-      <c r="C131" s="12">
-        <v>182167</v>
+      <c r="C131" s="5">
+        <v>174438</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -5835,11 +5832,11 @@
         <v>128</v>
       </c>
       <c r="B132" s="1"/>
-      <c r="C132" s="12">
-        <v>186725</v>
+      <c r="C132" s="5">
+        <v>182167</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -5866,11 +5863,11 @@
         <v>129</v>
       </c>
       <c r="B133" s="1"/>
-      <c r="C133" s="12">
-        <v>186901</v>
+      <c r="C133" s="5">
+        <v>186725</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -5897,11 +5894,11 @@
         <v>130</v>
       </c>
       <c r="B134" s="1"/>
-      <c r="C134" s="12">
-        <v>191858</v>
+      <c r="C134" s="5">
+        <v>186901</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -5928,11 +5925,11 @@
         <v>131</v>
       </c>
       <c r="B135" s="1"/>
-      <c r="C135" s="12">
-        <v>192738</v>
+      <c r="C135" s="5">
+        <v>191858</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
@@ -5959,8 +5956,8 @@
         <v>132</v>
       </c>
       <c r="B136" s="1"/>
-      <c r="C136" s="12">
-        <v>192739</v>
+      <c r="C136" s="5">
+        <v>192738</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>95</v>
@@ -5990,8 +5987,8 @@
         <v>133</v>
       </c>
       <c r="B137" s="1"/>
-      <c r="C137" s="12">
-        <v>192740</v>
+      <c r="C137" s="5">
+        <v>192739</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>95</v>
@@ -6021,8 +6018,8 @@
         <v>134</v>
       </c>
       <c r="B138" s="1"/>
-      <c r="C138" s="12">
-        <v>192741</v>
+      <c r="C138" s="5">
+        <v>192740</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>95</v>
@@ -6052,11 +6049,11 @@
         <v>135</v>
       </c>
       <c r="B139" s="1"/>
-      <c r="C139" s="12">
-        <v>202880</v>
+      <c r="C139" s="5">
+        <v>192741</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -6083,11 +6080,11 @@
         <v>136</v>
       </c>
       <c r="B140" s="1"/>
-      <c r="C140" s="12">
-        <v>266537</v>
+      <c r="C140" s="5">
+        <v>202880</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -6114,13 +6111,13 @@
         <v>137</v>
       </c>
       <c r="B141" s="1"/>
-      <c r="C141" s="12">
-        <v>286443</v>
+      <c r="C141" s="5">
+        <v>266537</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E141" s="7">
+        <v>127</v>
+      </c>
+      <c r="E141" s="1">
         <v>0</v>
       </c>
       <c r="F141" s="1"/>
@@ -6145,11 +6142,11 @@
         <v>138</v>
       </c>
       <c r="B142" s="1"/>
-      <c r="C142" s="12">
-        <v>323565</v>
+      <c r="C142" s="5">
+        <v>286443</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="E142" s="7">
         <v>0</v>
@@ -6176,11 +6173,11 @@
         <v>139</v>
       </c>
       <c r="B143" s="1"/>
-      <c r="C143" s="12">
-        <v>351369</v>
+      <c r="C143" s="5">
+        <v>323565</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E143" s="7">
         <v>0</v>
@@ -6207,11 +6204,11 @@
         <v>140</v>
       </c>
       <c r="B144" s="1"/>
-      <c r="C144" s="12">
-        <v>363651</v>
+      <c r="C144" s="5">
+        <v>351369</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="E144" s="7">
         <v>0</v>
@@ -6238,11 +6235,11 @@
         <v>141</v>
       </c>
       <c r="B145" s="1"/>
-      <c r="C145" s="12">
-        <v>374517</v>
+      <c r="C145" s="5">
+        <v>363651</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="E145" s="7">
         <v>0</v>
@@ -6269,11 +6266,11 @@
         <v>142</v>
       </c>
       <c r="B146" s="1"/>
-      <c r="C146" s="12">
-        <v>384900</v>
+      <c r="C146" s="5">
+        <v>374517</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E146" s="7">
         <v>0</v>
@@ -6300,11 +6297,11 @@
         <v>143</v>
       </c>
       <c r="B147" s="1"/>
-      <c r="C147" s="12">
-        <v>390760</v>
+      <c r="C147" s="5">
+        <v>384900</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="E147" s="7">
         <v>0</v>
@@ -6331,13 +6328,13 @@
         <v>144</v>
       </c>
       <c r="B148" s="1"/>
-      <c r="C148" s="12">
-        <v>457460</v>
+      <c r="C148" s="5">
+        <v>390760</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E148" s="1">
+        <v>80</v>
+      </c>
+      <c r="E148" s="7">
         <v>0</v>
       </c>
       <c r="F148" s="1"/>
@@ -6358,11 +6355,19 @@
       <c r="U148" s="1"/>
     </row>
     <row r="149" ht="17.25" spans="1:21">
-      <c r="A149" s="1"/>
+      <c r="A149" s="1">
+        <v>145</v>
+      </c>
       <c r="B149" s="1"/>
-      <c r="C149" s="12"/>
-      <c r="D149" s="1"/>
-      <c r="E149" s="1"/>
+      <c r="C149" s="5">
+        <v>457460</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E149" s="1">
+        <v>0</v>
+      </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
@@ -6380,10 +6385,10 @@
       <c r="T149" s="1"/>
       <c r="U149" s="1"/>
     </row>
-    <row r="150" spans="1:21">
+    <row r="150" ht="17.25" spans="1:21">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
-      <c r="C150" s="1"/>
+      <c r="C150" s="5"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
@@ -7967,6 +7972,29 @@
       <c r="T218" s="1"/>
       <c r="U218" s="1"/>
     </row>
+    <row r="219" spans="1:21">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
+      <c r="E219" s="1"/>
+      <c r="F219" s="1"/>
+      <c r="G219" s="1"/>
+      <c r="H219" s="1"/>
+      <c r="I219" s="1"/>
+      <c r="J219" s="1"/>
+      <c r="K219" s="1"/>
+      <c r="L219" s="1"/>
+      <c r="M219" s="1"/>
+      <c r="N219" s="1"/>
+      <c r="O219" s="1"/>
+      <c r="P219" s="1"/>
+      <c r="Q219" s="1"/>
+      <c r="R219" s="1"/>
+      <c r="S219" s="1"/>
+      <c r="T219" s="1"/>
+      <c r="U219" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
